--- a/DataTables/Datas/__pnlenums__.xlsx
+++ b/DataTables/Datas/__pnlenums__.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>设置界面</t>
+  </si>
+  <si>
+    <t>BattlePanel</t>
+  </si>
+  <si>
+    <t>战斗界面</t>
   </si>
 </sst>
 </file>
@@ -1054,8 +1060,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1179,6 +1185,17 @@
         <v>23</v>
       </c>
     </row>
+    <row r="6" spans="8:11">
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/DataTables/Datas/__pnlenums__.xlsx
+++ b/DataTables/Datas/__pnlenums__.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,12 @@
   </si>
   <si>
     <t>战斗界面</t>
+  </si>
+  <si>
+    <t>LoadingPanel</t>
+  </si>
+  <si>
+    <t>加载界面</t>
   </si>
 </sst>
 </file>
@@ -1060,8 +1066,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1196,6 +1202,17 @@
         <v>25</v>
       </c>
     </row>
+    <row r="7" spans="8:11">
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
